--- a/tests/regression_artifacts/downloads/email_03152025_RECEIPT/current/HAWB9600998.xlsx
+++ b/tests/regression_artifacts/downloads/email_03152025_RECEIPT/current/HAWB9600998.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Invoice Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invoice Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -767,19 +767,19 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>HATS AND OTHER HEADGEAR, PLAITED OR MADE BY ASSEMBLING STRIPS</t>
+          <t>Headgear</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>65040000</t>
+          <t>65000090</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>65040000</t>
+          <t>65000090</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       <c r="AJ2" s="2" t="n"/>
       <c r="AK2" s="2" t="inlineStr">
         <is>
-          <t>65040000</t>
+          <t>65000090</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>65040000</t>
+          <t>65000090</t>
         </is>
       </c>
       <c r="G3" s="4" t="n"/>
@@ -1599,7 +1599,7 @@
       <c r="I22" s="13" t="n"/>
       <c r="J22" s="14" t="inlineStr">
         <is>
-          <t>CET (20%) — Tariff 65040000</t>
+          <t>CET (20%) — Tariff 65000090</t>
         </is>
       </c>
       <c r="K22" s="13" t="n"/>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="F34" s="21" t="inlineStr">
         <is>
-          <t>62046290</t>
+          <t>62034290</t>
         </is>
       </c>
       <c r="G34" s="21" t="n"/>
@@ -2261,12 +2261,12 @@
       <c r="D37" s="21" t="n"/>
       <c r="E37" s="21" t="inlineStr">
         <is>
-          <t>HATS AND OTHER HEADGEAR, PLAITED OR MADE BY ASSEMBLING STRIPS</t>
+          <t>Headgear</t>
         </is>
       </c>
       <c r="F37" s="21" t="inlineStr">
         <is>
-          <t>65040000</t>
+          <t>65000090</t>
         </is>
       </c>
       <c r="G37" s="21" t="n"/>
